--- a/data/Sample.xlsx
+++ b/data/Sample.xlsx
@@ -482,8 +482,8 @@
       <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="I2">
-        <v>0</v>
+      <c r="I2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
